--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clément joue à l'aire de jeux, près de maman. Le sable est un peu chaud. Clément a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Clément verse le sable. Ça fait chh. Une feuille passe. Maman dit : c'est l'heure. On va reprendre ses affaires avant de partir. Clément cherche le seau. Il le prend. Clément cherche le manteau. Il le prend. Clément cherche le doudou. Il le prend. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Maman dit : merci Clément. C'était avant de partir. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté.</t>
+          <t>Clément joue à l'aire de jeux, près de maman. Le sable est un peu chaud. Clément a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Clément verse le sable. Ça fait chh. Une feuille passe. C'est l'heure. On va reprendre ses affaires avant de partir. Clément cherche le seau. Il le prend. Clément cherche le manteau. Il le prend. Clément cherche le doudou. Il le prend. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Merci Clément. C'était avant de partir. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clément joue à l'aire de jeux, près de maman. Le sable est un peu chaud. Clément a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Clément verse le sable. Ça fait chh. Une feuille passe.
+maman|C'est l'heure. On va reprendre ses affaires avant de partir.
+narrateur|Clément cherche le seau. Il le prend. Clément cherche le manteau. Il le prend. Clément cherche le doudou. Il le prend. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer.
+maman|Merci Clément. C'était avant de partir.
+narrateur|Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Avant de partir, que fait Clément ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Clément a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clément tient le seau. Maman ouvre la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Avant de partir, que fait Clément ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Clément a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était avant de partir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Clément tient le seau. Maman ouvre la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clément reprend ses affaires à l'aire de jeux</t>
+          <t>La feuille sur la vitre</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AUT.RAN.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>À l'aire de jeux, une feuille danse. Nino reprend seau, manteau et doudou avant de rentrer.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clément joue à l'aire de jeux, près de maman. Le sable est un peu chaud. Clément a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Clément verse le sable. Ça fait chh. Une feuille passe. C'est l'heure. On va reprendre ses affaires avant de partir. Clément cherche le seau. Il le prend. Clément cherche le manteau. Il le prend. Clément cherche le doudou. Il le prend. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Merci Clément. C'était avant de partir. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté.</t>
+          <t>Une feuille collée à la vitre tapote doucement. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Le seau reste vert, un peu sableux. C'est l'heure. On reprend tes affaires avant de partir. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. Nino cherche le seau. Il le prend. J'ai le seau. Bravo. Tu cherches le manteau ? Nino cherche le manteau. Il le prend. Le manteau est bleu. Et l'ours ? Nino cherche le doudou. Il le prend. L'ours est là. Merci, Nino. C'était avant de partir. Tu as repris tes affaires. Tu as fait du bon travail. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1329,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clément joue à l'aire de jeux, près de maman. Le sable est un peu chaud. Clément a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Clément verse le sable. Ça fait chh. Une feuille passe.
-maman|C'est l'heure. On va reprendre ses affaires avant de partir.
-narrateur|Clément cherche le seau. Il le prend. Clément cherche le manteau. Il le prend. Clément cherche le doudou. Il le prend. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer.
-maman|Merci Clément. C'était avant de partir.
-narrateur|Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté.</t>
+          <t>narrateur|Une feuille collée à la vitre tapote doucement.
+narrateur|Toc, toc.
+narrateur|Le soleil de l'après-midi la rend orange.
+narrateur|Maman ouvre un peu la fenêtre.
+narrateur|Un souffle d'air entre.
+maman|Tu as vu la feuille, Nino ?
+enfant-m|Elle est orange.
+maman|Elle veut rentrer.
+narrateur|Maman la pose sur le rebord.
+narrateur|En ce moment, Nino est à l'aire de jeux.
+narrateur|Le sable est un peu chaud.
+narrateur|Maman s'assoit au bord.
+narrateur|Nino a un seau vert.
+narrateur|Il a un manteau bleu posé au bord.
+narrateur|Il a son doudou ours.
+narrateur|Nino verse le sable.
+narrateur|Ça fait chh.
+narrateur|Une feuille passe.
+enfant-m|Une feuille, maman !
+maman|Comme celle de la fenêtre.
+maman|Elle danse.
+narrateur|La feuille se pose dans le seau.
+narrateur|Nino la sort tout doux.
+narrateur|Le seau reste vert, un peu sableux.
+maman|C'est l'heure.
+maman|On reprend tes affaires avant de partir.
+enfant-m|La feuille aussi ?
+maman|La feuille peut voler.
+maman|Tes affaires viennent à la maison.
+narrateur|Nino cherche le seau.
+narrateur|Il le prend.
+enfant-m|J'ai le seau.
+maman|Bravo.
+maman|Tu cherches le manteau ?
+narrateur|Nino cherche le manteau.
+narrateur|Il le prend.
+enfant-m|Le manteau est bleu.
+maman|Et l'ours ?
+narrateur|Nino cherche le doudou.
+narrateur|Il le prend.
+enfant-m|L'ours est là.
+maman|Merci, Nino.
+maman|C'était avant de partir.
+maman|Tu as repris tes affaires.
+maman|Tu as fait du bon travail.
+narrateur|Ses affaires sont dans ses bras.
+narrateur|Parce qu'il a repris ses affaires, on peut rentrer.
+narrateur|Ils marchent vers la maison.
+narrateur|Le seau cogne un peu.
+narrateur|Le doudou est contre lui.
+maman|Je marche à côté.
+enfant-m|Moi aussi.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Avant de partir, que fait Clément ?</t>
+          <t>Avant de partir, que fait Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,10 +1572,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Avant de partir, que fait Clément ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Avant de partir, que fait Nino ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Clément a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était avant de partir.</t>
+          <t>Nino a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était avant de partir. Tu as tout, Nino ? Oui, maman. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,10 +1743,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Clément a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a cherché.
+narrateur|Il a repris le seau.
+narrateur|Il a repris le manteau.
+narrateur|Il a repris le doudou.
+narrateur|C'était avant de partir.
+maman|Tu as tout, Nino ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clément tient le seau. Maman ouvre la porte.</t>
+          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près des chaussures ? Nino pose le seau. Il pose le manteau. L'ours reste dans son bras. Merci. Tu as repris tes affaires avant de partir. La vitre est calme. Plus de toc, toc.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1914,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clément tient le seau. Maman ouvre la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino tient le seau.
+narrateur|Maman ouvre la porte.
+narrateur|La feuille du rebord est encore là.
+enfant-m|Elle a attendu.
+maman|Oui.
+maman|Tu poses le seau près des chaussures ?
+narrateur|Nino pose le seau.
+narrateur|Il pose le manteau.
+narrateur|L'ours reste dans son bras.
+maman|Merci.
+maman|Tu as repris tes affaires avant de partir.
+narrateur|La vitre est calme.
+narrateur|Plus de toc, toc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1953,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai repris mes affaires. Avant de partir. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2093,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai repris mes affaires.
+maman|Avant de partir.
+maman|Bravo, Nino.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille collée à la vitre tapote doucement. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Le seau reste vert, un peu sableux. C'est l'heure. On reprend tes affaires avant de partir. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. Nino cherche le seau. Il le prend. J'ai le seau. Bravo. Tu cherches le manteau ? Nino cherche le manteau. Il le prend. Le manteau est bleu. Et l'ours ? Nino cherche le doudou. Il le prend. L'ours est là. Merci, Nino. C'était avant de partir. Tu as repris tes affaires. Tu as fait du bon travail. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
+          <t>Une feuille collée à la vitre tapote doucement. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. On va à l'aire de jeux ? Oui, maman. Ils prennent le sac. La rue est calme. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Le petit toboggan est tiède. Il est chaud, maman. Le soleil l'a touché. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Le seau reste vert, un peu sableux. C'est l'heure. On reprend tes affaires avant de partir. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. Nino cherche le seau. Il le prend. J'ai le seau. Bravo. Tu cherches le manteau ? Nino cherche le manteau. Il le prend. Le manteau est bleu. Et l'ours ? Nino cherche le doudou. Il le prend. L'ours est là. Merci, Nino. C'était avant de partir. Tu as repris tes affaires. Tu as fait du bon travail. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1338,12 +1338,19 @@
 enfant-m|Elle est orange.
 maman|Elle veut rentrer.
 narrateur|Maman la pose sur le rebord.
+maman|On va à l'aire de jeux ?
+enfant-m|Oui, maman.
+narrateur|Ils prennent le sac.
+narrateur|La rue est calme.
 narrateur|En ce moment, Nino est à l'aire de jeux.
 narrateur|Le sable est un peu chaud.
 narrateur|Maman s'assoit au bord.
 narrateur|Nino a un seau vert.
 narrateur|Il a un manteau bleu posé au bord.
 narrateur|Il a son doudou ours.
+narrateur|Le petit toboggan est tiède.
+enfant-m|Il est chaud, maman.
+maman|Le soleil l'a touché.
 narrateur|Nino verse le sable.
 narrateur|Ça fait chh.
 narrateur|Une feuille passe.
@@ -1778,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près des chaussures ? Nino pose le seau. Il pose le manteau. L'ours reste dans son bras. Merci. Tu as repris tes affaires avant de partir. La vitre est calme. Plus de toc, toc.</t>
+          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près des chaussures ? Nino pose le seau. Il pose le manteau. L'ours reste dans son bras. Merci. Tu as repris tes affaires avant de partir. La vitre est calme. Plus de toc, toc. Tu as repris tes affaires. Avant de partir. Oui. L'ours est contre Nino.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1926,7 +1933,11 @@
 maman|Merci.
 maman|Tu as repris tes affaires avant de partir.
 narrateur|La vitre est calme.
-narrateur|Plus de toc, toc.</t>
+narrateur|Plus de toc, toc.
+maman|Tu as repris tes affaires.
+enfant-m|Avant de partir.
+maman|Oui.
+narrateur|L'ours est contre Nino.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2171,41 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La feuille sur la vitre</t>
+          <t>La feuille qui danse</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>À l'aire de jeux, une feuille danse. Nino reprend seau, manteau et doudou avant de rentrer.</t>
+          <t>Nino veut garder une feuille qui danse dans son seau vert. Elle s'envole. Il reprend seau, manteau et ours pour lui faire une place près de la feuille de la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille collée à la vitre tapote doucement. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. On va à l'aire de jeux ? Oui, maman. Ils prennent le sac. La rue est calme. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Le petit toboggan est tiède. Il est chaud, maman. Le soleil l'a touché. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Le seau reste vert, un peu sableux. C'est l'heure. On reprend tes affaires avant de partir. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. Nino cherche le seau. Il le prend. J'ai le seau. Bravo. Tu cherches le manteau ? Nino cherche le manteau. Il le prend. Le manteau est bleu. Et l'ours ? Nino cherche le doudou. Il le prend. L'ours est là. Merci, Nino. C'était avant de partir. Tu as repris tes affaires. Tu as fait du bon travail. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
+          <t>Une feuille collée à la vitre tapote. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. On va à l'aire de jeux ? Oui, maman. Je veux une feuille, moi aussi. On regardera. Ils prennent le sac. La rue est calme. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Le petit toboggan est tiède. Il est chaud, maman. Le soleil l'a touché. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Elle habite ici. Le vent reprend la feuille. Elle s'envole au-dessus du bac. Elle est partie. Elle vole encore. C'est l'heure. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. On reprend ses affaires, avant de partir. Nino cherche le seau. Le seau est encore vert, un peu sableux. Il le prend. J'ai le seau. Bien. On lui fera une place, à la maison. Le manteau est au bord. Une manche est à l'envers. L'ours est près du toboggan.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clément joue à l'aire de jeux, près de maman. Le sable est un peu chaud. Clément a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Clément verse le sable. Ça fait chh. Une feuille passe. Maman dit : c'est l'heure. On va &lt;emphasis level="moderate"&gt;reprendre&lt;/emphasis&gt; ses affaires avant de partir. Clément cherche le seau. Il le prend. Clément cherche le manteau. Il le prend. Clément cherche le doudou. Il le prend. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Maman dit : merci Clément. C'était avant de partir. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille collée à la vitre tapote. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. On va à l'aire de jeux ? Oui, maman. Je veux une feuille, moi aussi. On regardera. Ils prennent le sac. La rue est calme. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Le petit toboggan est tiède. Il est chaud, maman. Le soleil l'a touché. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Elle habite ici. Le vent reprend la feuille. Elle s'envole au-dessus du bac. Elle est partie. Elle vole encore. C'est l'heure. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. On reprend ses affaires, avant de partir. Nino cherche le seau. Le seau est encore vert, un peu sableux. Il le prend. J'ai le seau. Bien. On lui fera une place, à la maison. Le manteau est au bord. Une manche est à l'envers. L'ours est près du toboggan.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une feuille collée à la vitre tapote doucement.
+          <t>narrateur|Une feuille collée à la vitre tapote.
 narrateur|Toc, toc.
 narrateur|Le soleil de l'après-midi la rend orange.
 narrateur|Maman ouvre un peu la fenêtre.
@@ -1340,6 +1340,8 @@
 narrateur|Maman la pose sur le rebord.
 maman|On va à l'aire de jeux ?
 enfant-m|Oui, maman.
+enfant-m|Je veux une feuille, moi aussi.
+maman|On regardera.
 narrateur|Ils prennent le sac.
 narrateur|La rue est calme.
 narrateur|En ce moment, Nino est à l'aire de jeux.
@@ -1359,35 +1361,25 @@
 maman|Elle danse.
 narrateur|La feuille se pose dans le seau.
 narrateur|Nino la sort tout doux.
-narrateur|Le seau reste vert, un peu sableux.
+enfant-m|Elle habite ici.
+narrateur|Le vent reprend la feuille.
+narrateur|Elle s'envole au-dessus du bac.
+enfant-m|Elle est partie.
+maman|Elle vole encore.
 maman|C'est l'heure.
-maman|On reprend tes affaires avant de partir.
 enfant-m|La feuille aussi ?
 maman|La feuille peut voler.
 maman|Tes affaires viennent à la maison.
+maman|On reprend ses affaires, avant de partir.
 narrateur|Nino cherche le seau.
+narrateur|Le seau est encore vert, un peu sableux.
 narrateur|Il le prend.
 enfant-m|J'ai le seau.
-maman|Bravo.
-maman|Tu cherches le manteau ?
-narrateur|Nino cherche le manteau.
-narrateur|Il le prend.
-enfant-m|Le manteau est bleu.
-maman|Et l'ours ?
-narrateur|Nino cherche le doudou.
-narrateur|Il le prend.
-enfant-m|L'ours est là.
-maman|Merci, Nino.
-maman|C'était avant de partir.
-maman|Tu as repris tes affaires.
-maman|Tu as fait du bon travail.
-narrateur|Ses affaires sont dans ses bras.
-narrateur|Parce qu'il a repris ses affaires, on peut rentrer.
-narrateur|Ils marchent vers la maison.
-narrateur|Le seau cogne un peu.
-narrateur|Le doudou est contre lui.
-maman|Je marche à côté.
-enfant-m|Moi aussi.</t>
+maman|Bien.
+maman|On lui fera une place, à la maison.
+narrateur|Le manteau est au bord.
+narrateur|Une manche est à l'envers.
+narrateur|L'ours est près du toboggan.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1424,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;&lt;emphasis level="moderate"&gt;avant&lt;/emphasis&gt; de partir, que fait Clément ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Avant de partir, que fait Nino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1439,7 +1431,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>reprendre | ses affaires | il reprend | avant de partir</t>
+          <t>reprendre | ses affaires | il reprend | elle reprend | avant de partir</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1454,7 +1446,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il reprend ses affaires. Que fait Clément ?</t>
+          <t>Il reprend ses affaires. Que fait Nino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1606,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était avant de partir. Tu as tout, Nino ? Oui, maman. Bravo. C'est du bon travail.</t>
+          <t>Nino cherche le manteau. Il tourne la manche tout doux. Le manteau est bleu. Il le prend. Et l'ours ? Nino va près du toboggan. L'ours est tiède, comme le plastique. L'ours est là. Il le prend. Tu as repris tes affaires. Avant de partir. Oui. La feuille de la fenêtre t'attend. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clément a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était &lt;emphasis level="moderate"&gt;avant&lt;/emphasis&gt; de partir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino cherche le manteau. Il tourne la manche tout doux. Le manteau est bleu. Il le prend. Et l'ours ? Nino va près du toboggan. L'ours est tiède, comme le plastique. L'ours est là. Il le prend. Tu as repris tes affaires. Avant de partir. Oui. La feuille de la fenêtre t'attend. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,15 +1742,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino a cherché.
-narrateur|Il a repris le seau.
-narrateur|Il a repris le manteau.
-narrateur|Il a repris le doudou.
-narrateur|C'était avant de partir.
-maman|Tu as tout, Nino ?
-enfant-m|Oui, maman.
-maman|Bravo.
-maman|C'est du bon travail.</t>
+          <t>narrateur|Nino cherche le manteau.
+narrateur|Il tourne la manche tout doux.
+enfant-m|Le manteau est bleu.
+narrateur|Il le prend.
+maman|Et l'ours ?
+narrateur|Nino va près du toboggan.
+narrateur|L'ours est tiède, comme le plastique.
+enfant-m|L'ours est là.
+narrateur|Il le prend.
+maman|Tu as repris tes affaires.
+enfant-m|Avant de partir.
+maman|Oui.
+maman|La feuille de la fenêtre t'attend.
+narrateur|Ils marchent vers la maison.
+narrateur|Le seau cogne un peu.
+narrateur|Le doudou est contre lui.
+maman|Je marche à côté.
+enfant-m|Moi aussi.</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1786,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près des chaussures ? Nino pose le seau. Il pose le manteau. L'ours reste dans son bras. Merci. Tu as repris tes affaires avant de partir. La vitre est calme. Plus de toc, toc. Tu as repris tes affaires. Avant de partir. Oui. L'ours est contre Nino.</t>
+          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près de la fenêtre ? Nino pose le seau sous le rebord. Il pose le manteau. L'ours reste dans son bras. On met la feuille dans le seau ? Oui. Elle visite. Maman glisse la feuille orange. Elle tapote le fond. Toc. Elle danse plus. Ici, elle se repose. Bravo. Tu as repris tes affaires. La vitre est calme. Plus de toc, toc. L'ours regarde le seau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clément tient le seau. Maman ouvre la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près de la fenêtre ? Nino pose le seau sous le rebord. Il pose le manteau. L'ours reste dans son bras. On met la feuille dans le seau ? Oui. Elle visite. Maman glisse la feuille orange. Elle tapote le fond. Toc. Elle danse plus. Ici, elle se repose. Bravo. Tu as repris tes affaires. La vitre est calme. Plus de toc, toc. L'ours regarde le seau.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,18 +1927,23 @@
 narrateur|La feuille du rebord est encore là.
 enfant-m|Elle a attendu.
 maman|Oui.
-maman|Tu poses le seau près des chaussures ?
-narrateur|Nino pose le seau.
+maman|Tu poses le seau près de la fenêtre ?
+narrateur|Nino pose le seau sous le rebord.
 narrateur|Il pose le manteau.
 narrateur|L'ours reste dans son bras.
-maman|Merci.
-maman|Tu as repris tes affaires avant de partir.
+maman|On met la feuille dans le seau ?
+enfant-m|Oui.
+enfant-m|Elle visite.
+narrateur|Maman glisse la feuille orange.
+narrateur|Elle tapote le fond.
+narrateur|Toc.
+enfant-m|Elle danse plus.
+maman|Ici, elle se repose.
+maman|Bravo.
+maman|Tu as repris tes affaires.
 narrateur|La vitre est calme.
 narrateur|Plus de toc, toc.
-maman|Tu as repris tes affaires.
-enfant-m|Avant de partir.
-maman|Oui.
-narrateur|L'ours est contre Nino.</t>
+narrateur|L'ours regarde le seau.</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai repris mes affaires. Avant de partir. Bravo, Nino. L'histoire est finie.</t>
+          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,9 +2110,9 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai repris mes affaires.
-maman|Avant de partir.
-maman|Bravo, Nino.
+          <t>enfant-m|La feuille a sa place.
+maman|Et toi, tu as repris tes affaires.
+narrateur|Le seau vert reste sous la fenêtre.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2128,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2208,6 +2214,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -1970,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre. L'histoire est finie.</t>
+          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre. L'histoire est finie.</t>
+          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2112,8 +2112,7 @@
         <is>
           <t>enfant-m|La feuille a sa place.
 maman|Et toi, tu as repris tes affaires.
-narrateur|Le seau vert reste sous la fenêtre.
-narrateur|L'histoire est finie.</t>
+narrateur|Le seau vert reste sous la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2219,6 +2218,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>aire de jeux</t>
+          <t>fenêtre de la maison, puis aire de jeux</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clément, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-05.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino veut garder une feuille qui danse dans son seau vert. Elle s'envole. Il reprend seau, manteau et ours pour lui faire une place près de la feuille de la fenêtre.</t>
+          <t>Nino connaît le toc de la fenêtre. Un éclat de vitre cligne sur le verre. Il veut une feuille dans le seau vert, maintenant. Il plaque trop vite : la feuille s'envole, manche tordue, ours au toboggan. Il reprend seau, manteau, ours. Merci vécu. À la maison il veut glisser trop fort. Il refuse de foncer, retrouve l'éclat, pose le seau. La feuille tapote.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille collée à la vitre tapote. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. On va à l'aire de jeux ? Oui, maman. Je veux une feuille, moi aussi. On regardera. Ils prennent le sac. La rue est calme. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Le petit toboggan est tiède. Il est chaud, maman. Le soleil l'a touché. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Elle habite ici. Le vent reprend la feuille. Elle s'envole au-dessus du bac. Elle est partie. Elle vole encore. C'est l'heure. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. On reprend ses affaires, avant de partir. Nino cherche le seau. Le seau est encore vert, un peu sableux. Il le prend. J'ai le seau. Bien. On lui fera une place, à la maison. Le manteau est au bord. Une manche est à l'envers. L'ours est près du toboggan.</t>
+          <t>Une ombre orange traverse le plancher, lente. Elle grimpe le mur, jusqu'au rebord. Derrière le verre, une feuille tapote. Toc, toc. Le soleil d'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre, tiède. Tu as vu la feuille, Nino ? Elle danse ! Sur la vitre, un éclat de vitre cligne. Tu vois l'éclat ? Il brille, sur le verre. Maman pose la feuille sur le rebord. Je veux une feuille, maintenant ! Dans mon seau vert ! On va à l'aire de jeux. Ils prennent le sac, près de la porte. La rue sent le sable chaud. En ce moment, Nino pose le seau vert au bac. Le sable est tiède, un peu collant. Maman s'assoit au bord, à sa hauteur. Le bac du toboggan tiède sent le sable. Le manteau bleu attend au bord, plié. L'ours doudou s'appuie au petit toboggan. Le toboggan est chaud. Le soleil l'a touché. Nino verse le sable. Ça fait chh, dans le seau. Une feuille orange passe, basse. La mienne, maintenant ! Elle se pose dans le seau vert. Nino plaque la main dessus, vite. Le seau bascule. Du sable glisse, chaud. La feuille s'envole au-dessus du bac. Elle est partie ! Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Nino veut courir après la feuille. Il tire le seau et le manteau, ensemble. La manche se tord, à l'envers. L'ours bascule, près du toboggan. Ça reste coincé ! C'est l'heure. La feuille aussi ? La feuille peut voler. Toi, tu reprends le seau ? Nino cherche le seau. Le seau est vert, un peu sableux. Il le prend. J'ai le seau. Le manteau est au bord. Une manche est à l'envers. L'ours est près du toboggan. Tu poses le seau un moment ? Maman s'accroupit à sa hauteur. Tu regardes tes affaires ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille collée à la vitre tapote. Toc, toc. Le soleil de l'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre. Tu as vu la feuille, Nino ? Elle est orange. Elle veut rentrer. Maman la pose sur le rebord. On va à l'aire de jeux ? Oui, maman. Je veux une feuille, moi aussi. On regardera. Ils prennent le sac. La rue est calme. En ce moment, Nino est à l'aire de jeux. Le sable est un peu chaud. Maman s'assoit au bord. Nino a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Le petit toboggan est tiède. Il est chaud, maman. Le soleil l'a touché. Nino verse le sable. Ça fait chh. Une feuille passe. Une feuille, maman ! Comme celle de la fenêtre. Elle danse. La feuille se pose dans le seau. Nino la sort tout doux. Elle habite ici. Le vent reprend la feuille. Elle s'envole au-dessus du bac. Elle est partie. Elle vole encore. C'est l'heure. La feuille aussi ? La feuille peut voler. Tes affaires viennent à la maison. On reprend ses affaires, avant de partir. Nino cherche le seau. Le seau est encore vert, un peu sableux. Il le prend. J'ai le seau. Bien. On lui fera une place, à la maison. Le manteau est au bord. Une manche est à l'envers. L'ours est près du toboggan.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une ombre orange traverse le plancher, lente. Elle grimpe le mur, jusqu'au rebord. Derrière le verre, une feuille tapote. Toc, toc. Le soleil d'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre, tiède. Tu as vu la feuille, Nino ? Elle danse ! Sur la vitre, un &lt;emphasis level="moderate"&gt;éclat de vitre&lt;/emphasis&gt; cligne. Tu vois l'éclat ? Il brille, sur le verre. Maman pose la feuille sur le rebord. Je veux une feuille, maintenant ! Dans mon seau vert ! On va à l'aire de jeux. Ils prennent le sac, près de la porte. La rue sent le sable chaud. En ce moment, Nino pose le seau vert au bac. Le sable est tiède, un peu collant. Maman s'assoit au bord, à sa hauteur. Le bac du toboggan tiède sent le sable. Le manteau bleu attend au bord, plié. L'ours doudou s'appuie au petit toboggan. Le toboggan est chaud. Le soleil l'a touché. Nino verse le sable. Ça fait chh, dans le seau. Une feuille orange passe, basse. La mienne, maintenant ! Elle se pose dans le seau vert. Nino plaque la main dessus, vite. Le seau bascule. Du sable glisse, chaud. La feuille s'envole au-dessus du bac. Elle est partie ! Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Nino veut courir après la feuille. Il tire le seau et le manteau, ensemble. La manche se tord, à l'envers. L'ours bascule, près du toboggan. Ça reste coincé ! C'est l'heure. La feuille aussi ? La feuille peut voler. Toi, tu reprends le seau ? Nino cherche le seau. Le seau est vert, un peu sableux. Il le prend. J'ai le seau. Le manteau est au bord. Une manche est à l'envers. L'ours est près du toboggan. Tu poses le seau un moment ? Maman s'accroupit à sa hauteur. Tu regardes tes affaires ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Clément joue à l'aire de jeux, près de maman. Le sable est un peu chaud. Clément a un seau vert. Il a un manteau bleu posé au bord. Il a son doudou ours. Clément verse le sable. Ça fait chh. Une feuille passe. Maman dit : c'est l'heure. On va &lt;emphasis&gt;reprendre&lt;/emphasis&gt; ses affaires avant de partir. Clément cherche le seau. Il le prend. Clément cherche le manteau. Il le prend. Clément cherche le doudou. Il le prend. Ses affaires sont dans ses bras. Parce qu'il a repris ses affaires, on peut rentrer. Maman dit : merci Clément. C'était avant de partir. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Maman reste à côté. [pause]</t>
+          <t>Une ombre orange traverse le plancher, lente. Elle grimpe le mur, jusqu'au rebord. Derrière le verre, une feuille tapote. Toc, toc. Le soleil d'après-midi la rend orange. Maman ouvre un peu la fenêtre. Un souffle d'air entre, tiède. Tu as vu la feuille, Nino ? Elle danse ! Sur la vitre, un &lt;emphasis&gt;éclat de vitre&lt;/emphasis&gt; cligne. Tu vois l'éclat ? Il brille, sur le verre. Maman pose la feuille sur le rebord. Je veux une feuille, maintenant ! Dans mon seau vert ! On va à l'aire de jeux. Ils prennent le sac, près de la porte. La rue sent le sable chaud. En ce moment, Nino pose le seau vert au bac. Le sable est tiède, un peu collant. Maman s'assoit au bord, à sa hauteur. Le bac du toboggan tiède sent le sable. Le manteau bleu attend au bord, plié. L'ours doudou s'appuie au petit toboggan. Le toboggan est chaud. Le soleil l'a touché. Nino verse le sable. Ça fait chh, dans le seau. Une feuille orange passe, basse. La mienne, maintenant ! Elle se pose dans le seau vert. Nino plaque la main dessus, vite. Le seau bascule. Du sable glisse, chaud. La feuille s'envole au-dessus du bac. Elle est partie ! Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Nino veut courir après la feuille. Il tire le seau et le manteau, ensemble. La manche se tord, à l'envers. L'ours bascule, près du toboggan. Ça reste coincé ! C'est l'heure. La feuille aussi ? La feuille peut voler. Toi, tu reprends le seau ? Nino cherche le seau. Le seau est vert, un peu sableux. Il le prend. J'ai le seau. Le manteau est au bord. Une manche est à l'envers. L'ours est près du toboggan. Tu poses le seau un moment ? Maman s'accroupit à sa hauteur. Tu regardes tes affaires ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>reprendre</t>
+          <t>éclat de vitre</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,65 +1326,75 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience_curieuse puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_la_feuille_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une feuille collée à la vitre tapote.
+          <t>narrateur|Une ombre orange traverse le plancher, lente.
+narrateur|Elle grimpe le mur, jusqu'au rebord.
+narrateur|Derrière le verre, une feuille tapote.
 narrateur|Toc, toc.
-narrateur|Le soleil de l'après-midi la rend orange.
+narrateur|Le soleil d'après-midi la rend orange.
 narrateur|Maman ouvre un peu la fenêtre.
-narrateur|Un souffle d'air entre.
+narrateur|Un souffle d'air entre, tiède.
 maman|Tu as vu la feuille, Nino ?
-enfant-m|Elle est orange.
-maman|Elle veut rentrer.
-narrateur|Maman la pose sur le rebord.
-maman|On va à l'aire de jeux ?
-enfant-m|Oui, maman.
-enfant-m|Je veux une feuille, moi aussi.
-maman|On regardera.
-narrateur|Ils prennent le sac.
-narrateur|La rue est calme.
-narrateur|En ce moment, Nino est à l'aire de jeux.
-narrateur|Le sable est un peu chaud.
-narrateur|Maman s'assoit au bord.
-narrateur|Nino a un seau vert.
-narrateur|Il a un manteau bleu posé au bord.
-narrateur|Il a son doudou ours.
-narrateur|Le petit toboggan est tiède.
-enfant-m|Il est chaud, maman.
+enfant-m|Elle danse !
+narrateur|Sur la vitre, un éclat de vitre cligne.
+maman|Tu vois l'éclat ?
+enfant-m|Il brille, sur le verre.
+narrateur|Maman pose la feuille sur le rebord.
+enfant-m|Je veux une feuille, maintenant !
+enfant-m|Dans mon seau vert !
+maman|On va à l'aire de jeux.
+narrateur|Ils prennent le sac, près de la porte.
+narrateur|La rue sent le sable chaud.
+narrateur|En ce moment, Nino pose le seau vert au bac.
+narrateur|Le sable est tiède, un peu collant.
+narrateur|Maman s'assoit au bord, à sa hauteur.
+narrateur|Le bac du toboggan tiède sent le sable.
+narrateur|Le manteau bleu attend au bord, plié.
+narrateur|L'ours doudou s'appuie au petit toboggan.
+enfant-m|Le toboggan est chaud.
 maman|Le soleil l'a touché.
 narrateur|Nino verse le sable.
-narrateur|Ça fait chh.
-narrateur|Une feuille passe.
-enfant-m|Une feuille, maman !
-maman|Comme celle de la fenêtre.
-maman|Elle danse.
-narrateur|La feuille se pose dans le seau.
-narrateur|Nino la sort tout doux.
-enfant-m|Elle habite ici.
-narrateur|Le vent reprend la feuille.
-narrateur|Elle s'envole au-dessus du bac.
-enfant-m|Elle est partie.
-maman|Elle vole encore.
+narrateur|Ça fait chh, dans le seau.
+narrateur|Une feuille orange passe, basse.
+enfant-m|La mienne, maintenant !
+narrateur|Elle se pose dans le seau vert.
+narrateur|Nino plaque la main dessus, vite.
+narrateur|Le seau bascule.
+narrateur|Du sable glisse, chaud.
+narrateur|La feuille s'envole au-dessus du bac.
+enfant-m|Elle est partie !
+narrateur|Le sourire de Nino disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Nino veut courir après la feuille.
+narrateur|Il tire le seau et le manteau, ensemble.
+narrateur|La manche se tord, à l'envers.
+narrateur|L'ours bascule, près du toboggan.
+enfant-m|Ça reste coincé !
 maman|C'est l'heure.
 enfant-m|La feuille aussi ?
 maman|La feuille peut voler.
-maman|Tes affaires viennent à la maison.
-maman|On reprend ses affaires, avant de partir.
+maman|Toi, tu reprends le seau ?
 narrateur|Nino cherche le seau.
-narrateur|Le seau est encore vert, un peu sableux.
+narrateur|Le seau est vert, un peu sableux.
 narrateur|Il le prend.
 enfant-m|J'ai le seau.
-maman|Bien.
-maman|On lui fera une place, à la maison.
 narrateur|Le manteau est au bord.
 narrateur|Une manche est à l'envers.
-narrateur|L'ours est près du toboggan.</t>
+narrateur|L'ours est près du toboggan.
+maman|Tu poses le seau un moment ?
+narrateur|Maman s'accroupit à sa hauteur.
+maman|Tu regardes tes affaires ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>fenetre,enfants_parc</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1421,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Avant de partir, que fait Nino ?</t>
+          <t>Nino prépare le départ. Le seau, le manteau, l'ours attendent. Avant de partir, que fait Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Avant de partir, que fait Nino ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino prépare le départ. Le seau, le manteau, l'ours attendent. &lt;emphasis level="moderate"&gt;Avant de partir&lt;/emphasis&gt;, que fait Nino ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;&lt;emphasis&gt;avant&lt;/emphasis&gt; de partir, que fait Clément ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nino prépare le départ. Le seau, le manteau, l'ours attendent. &lt;emphasis&gt;Avant de partir&lt;/emphasis&gt;, que fait Nino ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1484,7 +1494,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1495,7 +1505,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1510,38 +1520,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>avant</t>
+          <t>Avant de partir</t>
         </is>
       </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1556,22 +1566,24 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=avant_de_partir_il_reprend; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Avant de partir, que fait Nino ?</t>
+          <t>narrateur|Nino prépare le départ.
+narrateur|Le seau, le manteau, l'ours attendent.
+narrateur|Avant de partir, que fait Nino ?</t>
         </is>
       </c>
     </row>
@@ -1598,17 +1610,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino cherche le manteau. Il tourne la manche tout doux. Le manteau est bleu. Il le prend. Et l'ours ? Nino va près du toboggan. L'ours est tiède, comme le plastique. L'ours est là. Il le prend. Tu as repris tes affaires. Avant de partir. Oui. La feuille de la fenêtre t'attend. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
+          <t>Nino refuse de tirer plus fort. Il pose le seau vert, net. Je pose le seau. Nino reprend le manteau bleu. Il tourne la manche, lente. Le manteau est bleu. Il le passe, sans courir. Et l'ours ? Nino va près du toboggan. L'ours est tiède, comme le plastique. L'ours est là. Il reprend l'ours contre lui. Tu as tes affaires, Nino ? Oui, maman. Merci, Nino. On rentre vers la fenêtre ? Oui. Ils marchent vers la maison. Le seau cogne un peu, sableux. Contre lui, le doudou reste chaud. Je marche à côté. Moi aussi.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino cherche le manteau. Il tourne la manche tout doux. Le manteau est bleu. Il le prend. Et l'ours ? Nino va près du toboggan. L'ours est tiède, comme le plastique. L'ours est là. Il le prend. Tu as repris tes affaires. Avant de partir. Oui. La feuille de la fenêtre t'attend. Ils marchent vers la maison. Le seau cogne un peu. Le doudou est contre lui. Je marche à côté. Moi aussi.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino refuse de tirer plus fort. Il pose le seau vert, net. Je pose le seau. Nino reprend le &lt;emphasis level="moderate"&gt;manteau&lt;/emphasis&gt; bleu. Il tourne la manche, lente. Le manteau est bleu. Il le passe, sans courir. Et l'ours ? Nino va près du toboggan. L'ours est tiède, comme le plastique. L'ours est là. Il reprend l'ours contre lui. Tu as tes affaires, Nino ? Oui, maman. Merci, Nino. On rentre vers la fenêtre ? Oui. Ils marchent vers la maison. Le seau cogne un peu, sableux. Contre lui, le doudou reste chaud. Je marche à côté. Moi aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Clément a cherché. Il a repris le seau. Il a repris le manteau. Il a repris le doudou. C'était &lt;emphasis&gt;avant&lt;/emphasis&gt; de partir. [pause]</t>
+          <t>Nino refuse de tirer plus fort. Il pose le seau vert, net. Je pose le seau. Nino reprend le &lt;emphasis&gt;manteau&lt;/emphasis&gt; bleu. Il tourne la manche, lente. Le manteau est bleu. Il le passe, sans courir. Et l'ours ? Nino va près du toboggan. L'ours est tiède, comme le plastique. L'ours est là. Il reprend l'ours contre lui. Tu as tes affaires, Nino ? Oui, maman. Merci, Nino. On rentre vers la fenêtre ? Oui. Ils marchent vers la maison. Le seau cogne un peu, sableux. Contre lui, le doudou reste chaud. Je marche à côté. Moi aussi. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1666,7 +1678,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1701,7 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>avant</t>
+          <t>manteau</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
@@ -1703,16 +1715,16 @@
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1737,31 +1749,40 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=relancer; emotion=fierté_calme; intensite=1; destinataire=enfant; sous_texte=il_reprend_sans_foncer; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino cherche le manteau.
-narrateur|Il tourne la manche tout doux.
+          <t>narrateur|Nino refuse de tirer plus fort.
+narrateur|Il pose le seau vert, net.
+enfant-m|Je pose le seau.
+narrateur|Nino reprend le manteau bleu.
+narrateur|Il tourne la manche, lente.
 enfant-m|Le manteau est bleu.
-narrateur|Il le prend.
+narrateur|Il le passe, sans courir.
 maman|Et l'ours ?
 narrateur|Nino va près du toboggan.
 narrateur|L'ours est tiède, comme le plastique.
 enfant-m|L'ours est là.
-narrateur|Il le prend.
-maman|Tu as repris tes affaires.
-enfant-m|Avant de partir.
-maman|Oui.
-maman|La feuille de la fenêtre t'attend.
+narrateur|Il reprend l'ours contre lui.
+maman|Tu as tes affaires, Nino ?
+enfant-m|Oui, maman.
+maman|Merci, Nino.
+maman|On rentre vers la fenêtre ?
+enfant-m|Oui.
 narrateur|Ils marchent vers la maison.
-narrateur|Le seau cogne un peu.
-narrateur|Le doudou est contre lui.
+narrateur|Le seau cogne un peu, sableux.
+narrateur|Contre lui, le doudou reste chaud.
 maman|Je marche à côté.
 enfant-m|Moi aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>manteau,porte</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,17 +1807,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près de la fenêtre ? Nino pose le seau sous le rebord. Il pose le manteau. L'ours reste dans son bras. On met la feuille dans le seau ? Oui. Elle visite. Maman glisse la feuille orange. Elle tapote le fond. Toc. Elle danse plus. Ici, elle se repose. Bravo. Tu as repris tes affaires. La vitre est calme. Plus de toc, toc. L'ours regarde le seau.</t>
+          <t>Nino tient le seau, devant la porte. Maman ouvre. La feuille du rebord est là, orange. Elle a attendu ! Dans le seau, maintenant ! Il penche le seau trop vite. Du sable saute sur le rebord. La feuille bascule vers la fenêtre ouverte. Elle va partir ! Nino veut la rattraper d'un coup. Il refuse de foncer. Attends, je regarde. Maman attend, sans parler. Il observe le seau, puis la vitre. Sur le verre, un éclat de vitre cligne. C'est celui du début. Tu le vois, à la fenêtre ? Oui, il est resté. Nino pose le seau sous le rebord, lent. Il glisse la feuille orange, sans brusquer. Elle tapote le fond. Toc. Elle visite. Tu poses le manteau ? Nino pose le manteau près de la porte. L'ours reste dans son bras. La fenêtre se ferme un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nino tient le seau. Maman ouvre la porte. La feuille du rebord est encore là. Elle a attendu. Oui. Tu poses le seau près de la fenêtre ? Nino pose le seau sous le rebord. Il pose le manteau. L'ours reste dans son bras. On met la feuille dans le seau ? Oui. Elle visite. Maman glisse la feuille orange. Elle tapote le fond. Toc. Elle danse plus. Ici, elle se repose. Bravo. Tu as repris tes affaires. La vitre est calme. Plus de toc, toc. L'ours regarde le seau.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nino tient le seau, devant la porte. Maman ouvre. La feuille du rebord est là, orange. Elle a attendu ! Dans le seau, maintenant ! Il penche le seau trop vite. Du sable saute sur le rebord. La feuille bascule vers la fenêtre ouverte. Elle va partir ! Nino veut la rattraper d'un coup. Il refuse de foncer. Attends, je regarde. Maman attend, sans parler. Il observe le seau, puis la vitre. Sur le verre, un &lt;emphasis level="moderate"&gt;éclat de vitre&lt;/emphasis&gt; cligne. C'est celui du début. Tu le vois, à la fenêtre ? Oui, il est resté. Nino pose le seau sous le rebord, lent. Il glisse la feuille orange, sans brusquer. Elle tapote le fond. Toc. Elle visite. Tu poses le manteau ? Nino pose le manteau près de la porte. L'ours reste dans son bras. La fenêtre se ferme un peu.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Clément tient le seau. Maman ouvre la porte. [pause]</t>
+          <t>&lt;low-pitch&gt;Nino tient le seau, devant la porte. Maman ouvre. La feuille du rebord est là, orange. Elle a attendu ! Dans le seau, maintenant ! Il penche le seau trop vite. Du sable saute sur le rebord. La feuille bascule vers la fenêtre ouverte. Elle va partir ! Nino veut la rattraper d'un coup. Il refuse de foncer. Attends, je regarde. Maman attend, sans parler. Il observe le seau, puis la vitre. Sur le verre, un &lt;emphasis&gt;éclat de vitre&lt;/emphasis&gt; cligne. C'est celui du début. Tu le vois, à la fenêtre ? Oui, il est resté. Nino pose le seau sous le rebord, lent. Il glisse la feuille orange, sans brusquer. Elle tapote le fond. Toc. Elle visite. Tu poses le manteau ? Nino pose le manteau près de la porte. L'ours reste dans son bras. La fenêtre se ferme un peu.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1843,7 +1864,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1851,22 +1872,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1875,28 +1900,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de vitre</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1905,45 +1934,59 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_retrouve_l_eclat; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nino tient le seau.
-narrateur|Maman ouvre la porte.
-narrateur|La feuille du rebord est encore là.
-enfant-m|Elle a attendu.
-maman|Oui.
-maman|Tu poses le seau près de la fenêtre ?
-narrateur|Nino pose le seau sous le rebord.
-narrateur|Il pose le manteau.
-narrateur|L'ours reste dans son bras.
-maman|On met la feuille dans le seau ?
-enfant-m|Oui.
-enfant-m|Elle visite.
-narrateur|Maman glisse la feuille orange.
+          <t>narrateur|Nino tient le seau, devant la porte.
+narrateur|Maman ouvre.
+narrateur|La feuille du rebord est là, orange.
+enfant-m|Elle a attendu !
+enfant-m|Dans le seau, maintenant !
+narrateur|Il penche le seau trop vite.
+narrateur|Du sable saute sur le rebord.
+narrateur|La feuille bascule vers la fenêtre ouverte.
+enfant-m|Elle va partir !
+narrateur|Nino veut la rattraper d'un coup.
+narrateur|Il refuse de foncer.
+enfant-m|Attends, je regarde.
+narrateur|Maman attend, sans parler.
+narrateur|Il observe le seau, puis la vitre.
+narrateur|Sur le verre, un éclat de vitre cligne.
+enfant-m|C'est celui du début.
+maman|Tu le vois, à la fenêtre ?
+enfant-m|Oui, il est resté.
+narrateur|Nino pose le seau sous le rebord, lent.
+narrateur|Il glisse la feuille orange, sans brusquer.
 narrateur|Elle tapote le fond.
 narrateur|Toc.
-enfant-m|Elle danse plus.
-maman|Ici, elle se repose.
-maman|Bravo.
-maman|Tu as repris tes affaires.
-narrateur|La vitre est calme.
-narrateur|Plus de toc, toc.
-narrateur|L'ours regarde le seau.</t>
+enfant-m|Elle visite.
+maman|Tu poses le manteau ?
+narrateur|Nino pose le manteau près de la porte.
+narrateur|L'ours reste dans son bras.
+narrateur|La fenêtre se ferme un peu.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>porte</t>
         </is>
       </c>
     </row>
@@ -1970,17 +2013,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre.</t>
+          <t>La feuille a sa place. Le seau vert reste sous la fenêtre. Nino raccroche le manteau. Il est à sa place. Tu as fini de poser tes chaussures ? Oui, maman. La trace tiède de la paume a disparu. L'éclat de vitre reste, pâle, sur le verre. L'ours regarde le seau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La feuille a sa place. Et toi, tu as repris tes affaires. Le seau vert reste sous la fenêtre.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La feuille a sa place. Le seau vert reste sous la fenêtre. Nino raccroche le manteau. Il est à sa place. Tu as fini de poser tes chaussures ? Oui, maman. La trace tiède de la paume a disparu. L'&lt;emphasis level="moderate"&gt;éclat de vitre&lt;/emphasis&gt; reste, pâle, sur le verre. L'ours regarde le seau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La feuille a sa place. Le seau vert reste sous la fenêtre. Nino raccroche le manteau. Il est à sa place. Tu as fini de poser tes chaussures ? Oui, maman. La trace tiède de la paume a disparu. L'&lt;emphasis&gt;éclat de vitre&lt;/emphasis&gt; reste, pâle, sur le verre. L'ours regarde le seau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2027,7 +2070,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2035,10 +2078,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2047,12 +2090,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2061,17 +2104,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de vitre</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2080,11 +2127,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2093,26 +2140,41 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_reste_pale_le_seau_sous_la_fenetre; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>enfant-m|La feuille a sa place.
-maman|Et toi, tu as repris tes affaires.
-narrateur|Le seau vert reste sous la fenêtre.</t>
+narrateur|Le seau vert reste sous la fenêtre.
+narrateur|Nino raccroche le manteau.
+enfant-m|Il est à sa place.
+maman|Tu as fini de poser tes chaussures ?
+enfant-m|Oui, maman.
+narrateur|La trace tiède de la paume a disparu.
+narrateur|L'éclat de vitre reste, pâle, sur le verre.
+narrateur|L'ours regarde le seau.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>porte</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2225,6 +2287,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
